--- a/docs/StructureDefinition-VAERSImmunization.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-VAERSImmunization.xlsx
+++ b/docs/StructureDefinition-VAERSImmunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
